--- a/results/sl_optimization_summary.xlsx
+++ b/results/sl_optimization_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SL Optimization" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SL Optimization" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -47,7 +44,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -55,22 +52,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -471,47 +459,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>hold_days</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_trades</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>win_rate_pct</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>avg_return_pct</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>median_return_pct</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>stopped_out_pct</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_risk_pct</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>reward_risk</t>
         </is>
@@ -530,13 +518,13 @@
         <v>194</v>
       </c>
       <c r="D2" t="n">
-        <v>66.5</v>
+        <v>65.5</v>
       </c>
       <c r="E2" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="F2" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>29.4</v>
@@ -545,7 +533,7 @@
         <v>3.31</v>
       </c>
       <c r="I2" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="3">
@@ -561,13 +549,13 @@
         <v>194</v>
       </c>
       <c r="D3" t="n">
-        <v>63.9</v>
+        <v>63.4</v>
       </c>
       <c r="E3" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="F3" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="n">
         <v>19.1</v>
@@ -576,7 +564,7 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="4">
@@ -592,13 +580,13 @@
         <v>194</v>
       </c>
       <c r="D4" t="n">
-        <v>64.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="F4" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="G4" t="n">
         <v>12.4</v>
@@ -607,7 +595,7 @@
         <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -623,13 +611,13 @@
         <v>194</v>
       </c>
       <c r="D5" t="n">
-        <v>64.40000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="F5" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="G5" t="n">
         <v>17</v>
@@ -638,7 +626,7 @@
         <v>3.42</v>
       </c>
       <c r="I5" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="6">
@@ -654,13 +642,13 @@
         <v>194</v>
       </c>
       <c r="D6" t="n">
-        <v>59.8</v>
+        <v>59.3</v>
       </c>
       <c r="E6" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="F6" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G6" t="n">
         <v>26.8</v>
@@ -669,13 +657,13 @@
         <v>2.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fixed 5.0%</t>
+          <t>2.0x ATR</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -685,28 +673,28 @@
         <v>194</v>
       </c>
       <c r="D7" t="n">
-        <v>64.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="F7" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="G7" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4.56</v>
       </c>
       <c r="I7" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2.0x ATR</t>
+          <t>Fixed 5.0%</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -716,22 +704,22 @@
         <v>194</v>
       </c>
       <c r="D8" t="n">
-        <v>64.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="F8" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="G8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="H8" t="n">
-        <v>4.56</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="9">
@@ -747,13 +735,13 @@
         <v>194</v>
       </c>
       <c r="D9" t="n">
-        <v>57.2</v>
+        <v>56.7</v>
       </c>
       <c r="E9" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="F9" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="G9" t="n">
         <v>35.1</v>
@@ -762,7 +750,7 @@
         <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="10">
@@ -778,13 +766,13 @@
         <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>64.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="G10" t="n">
         <v>4.6</v>
@@ -809,13 +797,13 @@
         <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>64.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="F11" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="G11" t="n">
         <v>7.2</v>
@@ -840,13 +828,13 @@
         <v>194</v>
       </c>
       <c r="D12" t="n">
-        <v>64.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="F12" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="G12" t="n">
         <v>1.5</v>
@@ -855,7 +843,7 @@
         <v>10</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="13">
@@ -871,13 +859,13 @@
         <v>194</v>
       </c>
       <c r="D13" t="n">
-        <v>56.7</v>
+        <v>56.2</v>
       </c>
       <c r="E13" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="G13" t="n">
         <v>34</v>
@@ -886,7 +874,7 @@
         <v>2.28</v>
       </c>
       <c r="I13" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="14">
@@ -902,22 +890,22 @@
         <v>194</v>
       </c>
       <c r="D14" t="n">
-        <v>41.8</v>
+        <v>41.2</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="F14" t="n">
         <v>-1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>53.1</v>
+        <v>52.6</v>
       </c>
       <c r="H14" t="n">
         <v>1.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="15">
@@ -933,22 +921,22 @@
         <v>194</v>
       </c>
       <c r="D15" t="n">
-        <v>29.9</v>
+        <v>28.9</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="F15" t="n">
         <v>-1</v>
       </c>
       <c r="G15" t="n">
-        <v>69.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="16">
@@ -964,13 +952,13 @@
         <v>194</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>67.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="F16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="G16" t="n">
         <v>30.4</v>
@@ -998,10 +986,10 @@
         <v>62.9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="F17" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>23.2</v>
@@ -1029,10 +1017,10 @@
         <v>64.90000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="F18" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="G18" t="n">
         <v>17.5</v>
@@ -1063,7 +1051,7 @@
         <v>0.9</v>
       </c>
       <c r="F19" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="G19" t="n">
         <v>21.1</v>
@@ -1091,10 +1079,10 @@
         <v>64.90000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="F20" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="G20" t="n">
         <v>12.9</v>
@@ -1103,7 +1091,7 @@
         <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="21">
@@ -1122,10 +1110,10 @@
         <v>64.90000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="F21" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="G21" t="n">
         <v>13.4</v>
@@ -1153,10 +1141,10 @@
         <v>64.90000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="F22" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="G22" t="n">
         <v>8.199999999999999</v>
@@ -1184,7 +1172,7 @@
         <v>58.2</v>
       </c>
       <c r="E23" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="F23" t="n">
         <v>0.64</v>
@@ -1196,7 +1184,7 @@
         <v>2.5</v>
       </c>
       <c r="I23" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="24">
@@ -1215,10 +1203,10 @@
         <v>64.90000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="F24" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="G24" t="n">
         <v>5.2</v>
@@ -1246,10 +1234,10 @@
         <v>64.90000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="F25" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="G25" t="n">
         <v>2.1</v>
@@ -1277,7 +1265,7 @@
         <v>53.6</v>
       </c>
       <c r="E26" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="F26" t="n">
         <v>0.54</v>
@@ -1308,7 +1296,7 @@
         <v>55.7</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="F27" t="n">
         <v>0.59</v>
@@ -1336,10 +1324,10 @@
         <v>194</v>
       </c>
       <c r="D28" t="n">
-        <v>39.7</v>
+        <v>40.2</v>
       </c>
       <c r="E28" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="F28" t="n">
         <v>-1.5</v>
@@ -1351,7 +1339,7 @@
         <v>1.5</v>
       </c>
       <c r="I28" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="29">
@@ -1370,7 +1358,7 @@
         <v>28.9</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F29" t="n">
         <v>-1</v>
@@ -1382,7 +1370,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="30">
@@ -1398,13 +1386,13 @@
         <v>194</v>
       </c>
       <c r="D30" t="n">
-        <v>64.40000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="E30" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="F30" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="G30" t="n">
         <v>32.5</v>
@@ -1432,10 +1420,10 @@
         <v>62.9</v>
       </c>
       <c r="E31" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="F31" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="G31" t="n">
         <v>18.6</v>
@@ -1463,10 +1451,10 @@
         <v>60.3</v>
       </c>
       <c r="E32" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="F32" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="G32" t="n">
         <v>25.8</v>
@@ -1475,7 +1463,7 @@
         <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="33">
@@ -1494,10 +1482,10 @@
         <v>62.9</v>
       </c>
       <c r="E33" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="F33" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="G33" t="n">
         <v>8.800000000000001</v>
@@ -1506,7 +1494,7 @@
         <v>5.71</v>
       </c>
       <c r="I33" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="34">
@@ -1525,10 +1513,10 @@
         <v>61.9</v>
       </c>
       <c r="E34" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="F34" t="n">
-        <v>1.01</v>
+        <v>0.95</v>
       </c>
       <c r="G34" t="n">
         <v>24.2</v>
@@ -1537,7 +1525,7 @@
         <v>3.42</v>
       </c>
       <c r="I34" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35">
@@ -1556,10 +1544,10 @@
         <v>62.9</v>
       </c>
       <c r="E35" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="F35" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="G35" t="n">
         <v>14.4</v>
@@ -1587,10 +1575,10 @@
         <v>62.9</v>
       </c>
       <c r="E36" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="F36" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="G36" t="n">
         <v>13.9</v>
@@ -1618,10 +1606,10 @@
         <v>62.9</v>
       </c>
       <c r="E37" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="F37" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="G37" t="n">
         <v>2.1</v>
@@ -1649,10 +1637,10 @@
         <v>62.9</v>
       </c>
       <c r="E38" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="F38" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="G38" t="n">
         <v>6.2</v>
@@ -1661,7 +1649,7 @@
         <v>7</v>
       </c>
       <c r="I38" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="39">
@@ -1680,10 +1668,10 @@
         <v>57.2</v>
       </c>
       <c r="E39" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="G39" t="n">
         <v>35.1</v>
@@ -1692,7 +1680,7 @@
         <v>2.5</v>
       </c>
       <c r="I39" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="40">
@@ -1711,10 +1699,10 @@
         <v>54.1</v>
       </c>
       <c r="E40" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="F40" t="n">
-        <v>0.47</v>
+        <v>0.29</v>
       </c>
       <c r="G40" t="n">
         <v>40.7</v>
@@ -1723,7 +1711,7 @@
         <v>2.28</v>
       </c>
       <c r="I40" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="41">
@@ -1742,19 +1730,19 @@
         <v>52.1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G41" t="n">
-        <v>44.3</v>
+        <v>43.8</v>
       </c>
       <c r="H41" t="n">
         <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="42">
@@ -1770,10 +1758,10 @@
         <v>194</v>
       </c>
       <c r="D42" t="n">
-        <v>38.1</v>
+        <v>37.6</v>
       </c>
       <c r="E42" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="F42" t="n">
         <v>-1.5</v>
@@ -1785,7 +1773,7 @@
         <v>1.5</v>
       </c>
       <c r="I42" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="43">
@@ -1804,7 +1792,7 @@
         <v>26.8</v>
       </c>
       <c r="E43" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F43" t="n">
         <v>-1</v>
@@ -1816,7 +1804,7 @@
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
@@ -1829,25 +1817,25 @@
         <v>6</v>
       </c>
       <c r="C44" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D44" t="n">
-        <v>64</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="F44" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="G44" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="H44" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="I44" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="45">
@@ -1860,25 +1848,25 @@
         <v>6</v>
       </c>
       <c r="C45" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D45" t="n">
-        <v>60.8</v>
+        <v>61.3</v>
       </c>
       <c r="E45" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="F45" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="G45" t="n">
-        <v>22.8</v>
+        <v>22.2</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
       </c>
       <c r="I45" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="46">
@@ -1891,25 +1879,25 @@
         <v>6</v>
       </c>
       <c r="C46" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D46" t="n">
-        <v>57.1</v>
+        <v>57.7</v>
       </c>
       <c r="E46" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="F46" t="n">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="G46" t="n">
-        <v>29.6</v>
+        <v>28.9</v>
       </c>
       <c r="H46" t="n">
         <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="47">
@@ -1922,25 +1910,25 @@
         <v>6</v>
       </c>
       <c r="C47" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D47" t="n">
-        <v>62.4</v>
+        <v>62.9</v>
       </c>
       <c r="E47" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="F47" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="G47" t="n">
-        <v>16.4</v>
+        <v>16</v>
       </c>
       <c r="H47" t="n">
         <v>5</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="48">
@@ -1953,25 +1941,25 @@
         <v>6</v>
       </c>
       <c r="C48" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D48" t="n">
-        <v>58.7</v>
+        <v>59.3</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="F48" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="G48" t="n">
-        <v>27.5</v>
+        <v>26.8</v>
       </c>
       <c r="H48" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="I48" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="49">
@@ -1984,25 +1972,25 @@
         <v>6</v>
       </c>
       <c r="C49" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D49" t="n">
-        <v>61.4</v>
+        <v>61.9</v>
       </c>
       <c r="E49" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="F49" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="G49" t="n">
-        <v>19.6</v>
+        <v>19.1</v>
       </c>
       <c r="H49" t="n">
-        <v>4.55</v>
+        <v>4.56</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="50">
@@ -2015,25 +2003,25 @@
         <v>6</v>
       </c>
       <c r="C50" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D50" t="n">
-        <v>52.9</v>
+        <v>53.6</v>
       </c>
       <c r="E50" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="G50" t="n">
-        <v>38.1</v>
+        <v>37.1</v>
       </c>
       <c r="H50" t="n">
         <v>2.5</v>
       </c>
       <c r="I50" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="51">
@@ -2046,22 +2034,22 @@
         <v>6</v>
       </c>
       <c r="C51" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D51" t="n">
-        <v>62.4</v>
+        <v>62.9</v>
       </c>
       <c r="E51" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="G51" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="H51" t="n">
-        <v>5.69</v>
+        <v>5.71</v>
       </c>
       <c r="I51" t="n">
         <v>0.16</v>
@@ -2077,19 +2065,19 @@
         <v>6</v>
       </c>
       <c r="C52" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D52" t="n">
-        <v>62.4</v>
+        <v>62.9</v>
       </c>
       <c r="E52" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="G52" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H52" t="n">
         <v>7</v>
@@ -2108,25 +2096,25 @@
         <v>6</v>
       </c>
       <c r="C53" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D53" t="n">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="E53" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F53" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G53" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H53" t="n">
         <v>10</v>
       </c>
       <c r="I53" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="54">
@@ -2139,25 +2127,25 @@
         <v>6</v>
       </c>
       <c r="C54" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D54" t="n">
-        <v>50.8</v>
+        <v>51.5</v>
       </c>
       <c r="E54" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="F54" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="G54" t="n">
-        <v>45</v>
+        <v>43.8</v>
       </c>
       <c r="H54" t="n">
         <v>2.28</v>
       </c>
       <c r="I54" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="55">
@@ -2170,25 +2158,25 @@
         <v>6</v>
       </c>
       <c r="C55" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D55" t="n">
-        <v>48.1</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.22</v>
+        <v>-0.14</v>
       </c>
       <c r="G55" t="n">
-        <v>46.6</v>
+        <v>45.9</v>
       </c>
       <c r="H55" t="n">
         <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="56">
@@ -2201,25 +2189,25 @@
         <v>6</v>
       </c>
       <c r="C56" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D56" t="n">
-        <v>36.5</v>
+        <v>37.1</v>
       </c>
       <c r="E56" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="F56" t="n">
         <v>-1.5</v>
       </c>
       <c r="G56" t="n">
-        <v>62.4</v>
+        <v>61.9</v>
       </c>
       <c r="H56" t="n">
         <v>1.5</v>
       </c>
       <c r="I56" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="57">
@@ -2232,25 +2220,25 @@
         <v>6</v>
       </c>
       <c r="C57" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D57" t="n">
-        <v>25.4</v>
+        <v>25.8</v>
       </c>
       <c r="E57" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="F57" t="n">
         <v>-1</v>
       </c>
       <c r="G57" t="n">
-        <v>74.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="H57" t="n">
         <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="58">
@@ -2827,7 +2815,7 @@
         <v>57.9</v>
       </c>
       <c r="E76" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="F76" t="n">
         <v>1.48</v>
